--- a/IT_assets_data_import_template_2023.xlsx
+++ b/IT_assets_data_import_template_2023.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,15 +453,20 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>serial_number</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>eol_date</t>
         </is>
@@ -485,22 +490,23 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>jeli@tishmanspeyer.com</t>
+          <t>sli@tishmanspeyer.com</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
         <is>
           <t>024847395057</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>inUSE</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -525,17 +531,18 @@
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
         <is>
           <t>012587594857</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>inUSE</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -570,15 +577,20 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>juzhao@tishmanspeyer.com</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>018915404466</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>inUSE</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -603,17 +615,18 @@
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
         <is>
           <t>M70FHGLN</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>inUSE</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -648,15 +661,20 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>juzhao@tishmanspeyer.com</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>M70FHGLJ</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>inUSE</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -681,17 +699,18 @@
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
         <is>
           <t>021123581557</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>inUSE</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -716,17 +735,18 @@
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
         <is>
           <t>004494781757</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>inUSE</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
@@ -745,15 +765,20 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
+          <t>glu@contractors.tishmanspeyer.com</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>PC0RVBQZ</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
@@ -766,17 +791,18 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
         <is>
           <t>PC0QNXP7</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
@@ -797,17 +823,18 @@
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
         <is>
           <t>PC0QCQZ2</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>inUSE</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
@@ -824,17 +851,18 @@
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
         <is>
           <t>PC0EMX7K</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
@@ -847,17 +875,18 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
         <is>
           <t>R8XD6K7</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
@@ -870,17 +899,18 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
         <is>
           <t>ES09578606</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
@@ -897,17 +927,18 @@
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
         <is>
           <t>000860790257</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
@@ -934,15 +965,20 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
+          <t>eshen712@gmail.com</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
           <t>000289290657</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
